--- a/outputs/evaluation/architecture/design/v1/CF_M08/run_1/CF_M08_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v1/CF_M08/run_1/CF_M08_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.3548</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.3448</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5128</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9296</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8669</v>
       </c>
     </row>
@@ -1221,14 +1235,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Observer</t>
@@ -1247,14 +1258,11 @@
       <c r="P2" t="n">
         <v>66</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M08_P04</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1295,14 +1303,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Security Service</t>
@@ -1326,13 +1331,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M08_AU02</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1373,14 +1376,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>System Service</t>
@@ -1404,13 +1404,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1431,7 +1429,6 @@
       <c r="D5" t="n">
         <v>0.8669</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1452,7 +1449,6 @@
           <t>['AU_02', 'AU_03']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_08</t>
@@ -1463,7 +1459,6 @@
           <t>system service (next.js), data service (postgresql)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1482,7 +1477,6 @@
           <t>CF_M08_AU04, CF_M08_AU08</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M08_AU24</t>
@@ -1533,14 +1527,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Data Service</t>
@@ -1564,13 +1555,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M08_AU07</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1611,14 +1600,11 @@
           <t>67</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Singleton</t>
@@ -1637,14 +1623,11 @@
       <c r="P7" t="n">
         <v>67</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M08_P05</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1685,14 +1668,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Component-based</t>
@@ -1711,14 +1691,11 @@
       <c r="P8" t="n">
         <v>66</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M08_P03</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1764,13 +1741,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>React</t>
@@ -1794,13 +1769,11 @@
           <t>CF_M08_AU04</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M08_AU06</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1841,14 +1814,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Docker</t>
@@ -1872,13 +1842,11 @@
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M08_AU22</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1919,14 +1887,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Microservices</t>
@@ -1945,14 +1910,11 @@
       <c r="P11" t="n">
         <v>41</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M08_P01</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1998,13 +1960,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Prisma</t>
@@ -2028,13 +1988,11 @@
           <t>CF_M08_P02</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M08_AU09</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2103,7 +2061,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>security service (traefik), system service (next.js), data service (postgresql)</t>
@@ -2200,7 +2157,6 @@
           <t>Amazon EC2</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>These services run on Amazon EC2 instances</t>
@@ -2236,7 +2192,6 @@
           <t>Traefik</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Security Service (Traefik)</t>
@@ -2272,7 +2227,6 @@
           <t>Next.js</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>System Service (Next.js)</t>
@@ -2303,7 +2257,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>system service, authentication, cloud storage, payment processing, analytics, error monitoring, email</t>
@@ -2344,7 +2297,6 @@
           <t>PostgreSQL</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Communicates with the PostgreSQL database service (Data Service) using Prisma as ORM (Object-Relational Mapping).</t>
@@ -2380,7 +2332,6 @@
           <t>Authentication</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Authentication: Use Google for user authentication.</t>
@@ -2416,7 +2367,6 @@
           <t>Google</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Authentication: Use Google for user authentication.</t>
@@ -2452,7 +2402,6 @@
           <t>Cloud storage</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
@@ -2488,7 +2437,6 @@
           <t>Amazon S3</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Cloud storage: Use Amazon S3 to store and retrieve files.</t>
@@ -2524,7 +2472,6 @@
           <t>Payment processing</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
@@ -2560,7 +2507,6 @@
           <t>Stripe</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Payment processing: Integrates with Stripe to manage payments and subscriptions tions.</t>
@@ -2596,7 +2542,6 @@
           <t>Analytics</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Analytics: Implement Google Analytics to track and analyze the traffic of the site.</t>
@@ -2632,7 +2577,6 @@
           <t>Google Analytics</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Implement Google Analytics to track and analyze site traffic</t>
@@ -2668,7 +2612,6 @@
           <t>Error monitoring</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
@@ -2704,7 +2647,6 @@
           <t>Sentry</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>Error monitoring: Use Sentry to track and manage errors in the application.</t>
@@ -2740,7 +2682,6 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>Connects to Brevo to create, send and schedule emails electronics.</t>
@@ -2776,7 +2717,6 @@
           <t>Brevo</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>Connects to Brevo to create, send and schedule emails.</t>
@@ -2812,7 +2752,6 @@
           <t>HTTPS</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>HTTPS, which is the standard for secure communications on the web</t>
@@ -2848,7 +2787,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>(footnote) It is a programming technique to convert data between the type system used in an object-oriented programming language and the use of a relational database as a persistence engine (Atencio 2016).</t>
@@ -2884,7 +2822,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve"> The Revivack application mainly uses Next.js for system development, which allows to separate the components between client and server rendering</t>
